--- a/data/trans_orig/Hacinamiento_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2007</t>
+          <t>Hogares con dos o más personas por habitación en 2007 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6569</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23726</t>
+          <t>24908</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7311</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22348</t>
+          <t>22144</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18374</t>
+          <t>18417</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>41471</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>450050</t>
+          <t>448868</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>467207</t>
+          <t>465821</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283313</t>
+          <t>283517</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>298350</t>
+          <t>298254</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>738252</t>
+          <t>737966</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>761063</t>
+          <t>761020</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2938</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13283</t>
+          <t>13640</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26554</t>
+          <t>27458</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15463</t>
+          <t>14780</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35445</t>
+          <t>35232</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>352815</t>
+          <t>352458</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363160</t>
+          <t>363241</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>344372</t>
+          <t>343468</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>361131</t>
+          <t>360611</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>701579</t>
+          <t>701792</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>721561</t>
+          <t>722244</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18087</t>
+          <t>18384</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>37855</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19582</t>
+          <t>18078</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25632</t>
+          <t>27157</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49839</t>
+          <t>51040</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>501710</t>
+          <t>502367</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>522135</t>
+          <t>521838</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148200</t>
+          <t>149704</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162774</t>
+          <t>162840</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>658164</t>
+          <t>656963</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>682371</t>
+          <t>680846</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41141</t>
+          <t>41735</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70563</t>
+          <t>71682</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27799</t>
+          <t>28037</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53654</t>
+          <t>54683</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75185</t>
+          <t>75637</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113153</t>
+          <t>115189</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1165693</t>
+          <t>1164574</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1195115</t>
+          <t>1194521</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>660631</t>
+          <t>659602</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>686486</t>
+          <t>686248</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1837389</t>
+          <t>1835353</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1875357</t>
+          <t>1874905</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24276</t>
+          <t>23810</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47661</t>
+          <t>48365</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37743</t>
+          <t>38809</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67953</t>
+          <t>68955</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68919</t>
+          <t>68701</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>109155</t>
+          <t>105533</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>299460</t>
+          <t>298756</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>322845</t>
+          <t>323311</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>497951</t>
+          <t>496949</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>528161</t>
+          <t>527095</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>803870</t>
+          <t>807492</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>844106</t>
+          <t>844324</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,48%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12672</t>
+          <t>12722</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31277</t>
+          <t>30750</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53277</t>
+          <t>55091</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>86646</t>
+          <t>87402</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>73020</t>
+          <t>69090</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>109993</t>
+          <t>106460</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>265018</t>
+          <t>265545</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>283623</t>
+          <t>283573</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1158005</t>
+          <t>1157249</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1191374</t>
+          <t>1189560</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1430953</t>
+          <t>1434486</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1467926</t>
+          <t>1471856</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>134033</t>
+          <t>130325</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>183962</t>
+          <t>182809</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>174018</t>
+          <t>173285</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>231698</t>
+          <t>234536</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>319082</t>
+          <t>320135</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>398238</t>
+          <t>395088</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3075807</t>
+          <t>3076960</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3125736</t>
+          <t>3129444</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3137511</t>
+          <t>3134673</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3195191</t>
+          <t>3195924</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6230740</t>
+          <t>6233890</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6309896</t>
+          <t>6308843</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2012</t>
+          <t>Hogares con dos o más personas por habitación en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15788</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>8407</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22429</t>
+          <t>24944</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14176</t>
+          <t>14236</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32532</t>
+          <t>32494</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>421423</t>
+          <t>421757</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>433408</t>
+          <t>433456</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>292025</t>
+          <t>289510</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>306371</t>
+          <t>306047</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>719133</t>
+          <t>719171</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>737489</t>
+          <t>737429</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19389</t>
+          <t>19180</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12465</t>
+          <t>12115</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30346</t>
+          <t>29938</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21497</t>
+          <t>20797</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44583</t>
+          <t>44382</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>397037</t>
+          <t>397246</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>411245</t>
+          <t>411081</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>305478</t>
+          <t>305886</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>323359</t>
+          <t>323709</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>707667</t>
+          <t>707868</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>730753</t>
+          <t>731453</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23058</t>
+          <t>22709</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45884</t>
+          <t>45187</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8308</t>
+          <t>7787</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23008</t>
+          <t>22558</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35484</t>
+          <t>34832</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63328</t>
+          <t>62361</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>580488</t>
+          <t>581185</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>603314</t>
+          <t>603663</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>237121</t>
+          <t>237571</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>251821</t>
+          <t>252342</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>823174</t>
+          <t>824141</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>851018</t>
+          <t>851670</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53396</t>
+          <t>53098</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84983</t>
+          <t>84234</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45147</t>
+          <t>44304</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77178</t>
+          <t>75394</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>104234</t>
+          <t>105219</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>151496</t>
+          <t>150490</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1069097</t>
+          <t>1069846</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1100684</t>
+          <t>1100982</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>685205</t>
+          <t>686989</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>717236</t>
+          <t>718079</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1764967</t>
+          <t>1765973</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1812229</t>
+          <t>1811244</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24285</t>
+          <t>24083</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46486</t>
+          <t>46419</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41408</t>
+          <t>41896</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71263</t>
+          <t>71067</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72786</t>
+          <t>72091</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>110718</t>
+          <t>108117</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>463108</t>
+          <t>463175</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>485309</t>
+          <t>485511</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>686281</t>
+          <t>686477</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>716136</t>
+          <t>715648</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1156420</t>
+          <t>1159021</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1194352</t>
+          <t>1195047</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17091</t>
+          <t>16288</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44073</t>
+          <t>41842</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73119</t>
+          <t>70340</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51621</t>
+          <t>50643</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>83848</t>
+          <t>82905</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248477</t>
+          <t>249280</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261492</t>
+          <t>261438</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1032043</t>
+          <t>1034822</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1061089</t>
+          <t>1063320</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1286882</t>
+          <t>1287825</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1319109</t>
+          <t>1320087</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>139863</t>
+          <t>139027</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>187762</t>
+          <t>191687</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>191859</t>
+          <t>193070</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>249027</t>
+          <t>251427</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>344742</t>
+          <t>343533</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>423179</t>
+          <t>421614</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3221489</t>
+          <t>3217564</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3269388</t>
+          <t>3270224</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3286470</t>
+          <t>3284070</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3343638</t>
+          <t>3342427</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6521569</t>
+          <t>6523134</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6600006</t>
+          <t>6601215</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2016</t>
+          <t>Hogares con dos o más personas por habitación en 2016 (tasa de respuesta: 99,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3835</t>
+          <t>3789</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15804</t>
+          <t>15937</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8089</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22946</t>
+          <t>24467</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14729</t>
+          <t>13826</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33328</t>
+          <t>33531</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>412325</t>
+          <t>412192</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>424294</t>
+          <t>424340</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>322267</t>
+          <t>320746</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>337124</t>
+          <t>337170</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>740014</t>
+          <t>739811</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>758613</t>
+          <t>759516</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>6461</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20969</t>
+          <t>20829</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8635</t>
+          <t>7872</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24139</t>
+          <t>23282</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18023</t>
+          <t>17398</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38727</t>
+          <t>39985</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>352174</t>
+          <t>352314</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>366635</t>
+          <t>366682</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>346209</t>
+          <t>347066</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>361713</t>
+          <t>362476</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>704764</t>
+          <t>703506</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>725468</t>
+          <t>726093</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15127</t>
+          <t>15352</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36373</t>
+          <t>36151</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10455</t>
+          <t>9863</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19101</t>
+          <t>18455</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40605</t>
+          <t>41126</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>480131</t>
+          <t>480353</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>501377</t>
+          <t>501152</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155668</t>
+          <t>156260</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164899</t>
+          <t>164965</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>642022</t>
+          <t>641501</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>663526</t>
+          <t>664172</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31977</t>
+          <t>34306</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59710</t>
+          <t>61766</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31042</t>
+          <t>31363</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56800</t>
+          <t>56520</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70212</t>
+          <t>71344</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>108091</t>
+          <t>109199</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1083934</t>
+          <t>1081878</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1111667</t>
+          <t>1109338</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>763981</t>
+          <t>764261</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>789739</t>
+          <t>789418</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1856334</t>
+          <t>1855226</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1894213</t>
+          <t>1893081</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23708</t>
+          <t>22701</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49239</t>
+          <t>50094</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37853</t>
+          <t>37738</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63328</t>
+          <t>64565</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67334</t>
+          <t>66886</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101787</t>
+          <t>102754</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>569685</t>
+          <t>568830</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>595216</t>
+          <t>596223</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>670445</t>
+          <t>669208</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>695920</t>
+          <t>696035</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1250910</t>
+          <t>1249943</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1285363</t>
+          <t>1285811</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12177</t>
+          <t>12448</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30268</t>
+          <t>30772</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26380</t>
+          <t>25197</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51815</t>
+          <t>51153</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41915</t>
+          <t>43394</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>74286</t>
+          <t>73757</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255765</t>
+          <t>255261</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>273856</t>
+          <t>273585</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1025211</t>
+          <t>1025873</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1050646</t>
+          <t>1051829</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1288773</t>
+          <t>1289302</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1321144</t>
+          <t>1319665</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>123060</t>
+          <t>121007</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>171734</t>
+          <t>170070</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>138161</t>
+          <t>135480</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>187408</t>
+          <t>186277</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>273068</t>
+          <t>271569</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>343204</t>
+          <t>339396</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3194642</t>
+          <t>3196306</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3243316</t>
+          <t>3245369</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3325857</t>
+          <t>3326988</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3375104</t>
+          <t>3377785</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6536437</t>
+          <t>6540245</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6606573</t>
+          <t>6608072</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2023</t>
+          <t>Hogares con dos o más personas por habitación en 2023 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7436</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23215</t>
+          <t>21258</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17171</t>
+          <t>17258</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15148</t>
+          <t>14902</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34842</t>
+          <t>33654</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>475292</t>
+          <t>477249</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>491071</t>
+          <t>491518</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>427849</t>
+          <t>427762</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>440298</t>
+          <t>440429</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>908686</t>
+          <t>909874</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>928380</t>
+          <t>928626</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17569</t>
+          <t>15794</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>3046</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11183</t>
+          <t>11171</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6913</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21917</t>
+          <t>22189</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>430865</t>
+          <t>432640</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>446380</t>
+          <t>446334</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>365449</t>
+          <t>365461</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>373531</t>
+          <t>373586</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>803149</t>
+          <t>802877</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>818153</t>
+          <t>818920</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20948</t>
+          <t>21075</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8443</t>
+          <t>9929</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23247</t>
+          <t>24567</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>642805</t>
+          <t>642678</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>661334</t>
+          <t>661061</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155434</t>
+          <t>153948</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163386</t>
+          <t>163201</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>804383</t>
+          <t>803063</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>823427</t>
+          <t>823105</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15254</t>
+          <t>15209</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34326</t>
+          <t>35837</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6517</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25146</t>
+          <t>25536</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25985</t>
+          <t>26632</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54397</t>
+          <t>54843</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>999318</t>
+          <t>997807</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1018390</t>
+          <t>1018435</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>946562</t>
+          <t>946172</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>965191</t>
+          <t>965024</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1950955</t>
+          <t>1950509</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1979367</t>
+          <t>1978720</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>6876</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20484</t>
+          <t>21171</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16766</t>
+          <t>16982</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36076</t>
+          <t>34975</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27158</t>
+          <t>26086</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50971</t>
+          <t>48749</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>452390</t>
+          <t>451703</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>466053</t>
+          <t>465998</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>797044</t>
+          <t>798145</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>816354</t>
+          <t>816138</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1255022</t>
+          <t>1257244</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1278835</t>
+          <t>1279907</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11533</t>
+          <t>11062</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16395</t>
+          <t>16787</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45007</t>
+          <t>45249</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19005</t>
+          <t>18371</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48049</t>
+          <t>49545</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>221687</t>
+          <t>222158</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>709645</t>
+          <t>709403</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>738257</t>
+          <t>737865</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>939823</t>
+          <t>938327</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>968867</t>
+          <t>969501</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49502</t>
+          <t>50665</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89262</t>
+          <t>91407</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,82 +10711,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>84715</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>64608</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>108768</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>153301</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>126959</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>183299</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>2,66%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>84715</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>64633</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>107163</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>153301</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>128458</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>187108</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3261171</t>
+          <t>3259026</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3300931</t>
+          <t>3299768</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,82 +10824,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>97,27%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>98,49%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>5061</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>3460294</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>3436241</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3480401</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>97,61%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>96,93%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>8258</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>6742140</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>6712142</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>6768482</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>97,78%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>97,34%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>98,52%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>5061</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>3460294</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>3437846</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>3480376</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>97,61%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>96,98%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>8258</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>6742140</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>6708333</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>6766983</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>97,29%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Hacinamiento_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>7602</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24908</t>
+          <t>24729</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>8014</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22144</t>
+          <t>23703</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18417</t>
+          <t>18503</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41471</t>
+          <t>41224</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>448868</t>
+          <t>449047</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>465821</t>
+          <t>466174</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283517</t>
+          <t>281958</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>298254</t>
+          <t>297647</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>737966</t>
+          <t>738213</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>761020</t>
+          <t>760934</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13640</t>
+          <t>12344</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>10761</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27458</t>
+          <t>27816</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14780</t>
+          <t>15397</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35232</t>
+          <t>35268</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>352458</t>
+          <t>353754</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363241</t>
+          <t>363278</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>343468</t>
+          <t>343110</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>360611</t>
+          <t>360165</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>701792</t>
+          <t>701756</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>722244</t>
+          <t>721627</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18384</t>
+          <t>18092</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37855</t>
+          <t>37745</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>4978</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18078</t>
+          <t>18766</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27157</t>
+          <t>26585</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51040</t>
+          <t>50787</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>502367</t>
+          <t>502477</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>521838</t>
+          <t>522130</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149704</t>
+          <t>149016</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162840</t>
+          <t>162804</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>656963</t>
+          <t>657216</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>680846</t>
+          <t>681418</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41735</t>
+          <t>41357</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71682</t>
+          <t>71094</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28037</t>
+          <t>28493</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54683</t>
+          <t>53119</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75637</t>
+          <t>75929</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115189</t>
+          <t>114118</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1164574</t>
+          <t>1165162</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1194521</t>
+          <t>1194899</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>659602</t>
+          <t>661166</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>686248</t>
+          <t>685792</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1835353</t>
+          <t>1836424</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1874905</t>
+          <t>1874613</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23810</t>
+          <t>24267</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48365</t>
+          <t>49069</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38809</t>
+          <t>37672</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68955</t>
+          <t>67885</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68701</t>
+          <t>67887</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>105533</t>
+          <t>104041</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>298756</t>
+          <t>298052</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>323311</t>
+          <t>322854</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>496949</t>
+          <t>498019</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>527095</t>
+          <t>528232</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>807492</t>
+          <t>808984</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>844324</t>
+          <t>845138</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12722</t>
+          <t>12777</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30750</t>
+          <t>30125</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55091</t>
+          <t>55031</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87402</t>
+          <t>85827</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>69090</t>
+          <t>72351</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>106460</t>
+          <t>111425</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>265545</t>
+          <t>266170</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>283573</t>
+          <t>283518</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1157249</t>
+          <t>1158824</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1189560</t>
+          <t>1189620</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1434486</t>
+          <t>1429521</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1471856</t>
+          <t>1468595</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>130325</t>
+          <t>134064</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>182809</t>
+          <t>185889</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>173285</t>
+          <t>174628</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>234536</t>
+          <t>231020</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>320135</t>
+          <t>322692</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>395088</t>
+          <t>397651</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3076960</t>
+          <t>3073880</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3129444</t>
+          <t>3125705</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3134673</t>
+          <t>3138189</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3195924</t>
+          <t>3194581</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6233890</t>
+          <t>6231327</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6308843</t>
+          <t>6306286</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15454</t>
+          <t>14908</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8407</t>
+          <t>8725</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24944</t>
+          <t>24138</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14236</t>
+          <t>14181</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32494</t>
+          <t>32544</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>421757</t>
+          <t>422303</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>433456</t>
+          <t>433814</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>289510</t>
+          <t>290316</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>306047</t>
+          <t>305729</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>719171</t>
+          <t>719121</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>737429</t>
+          <t>737484</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>4965</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19180</t>
+          <t>18331</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12115</t>
+          <t>12924</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29938</t>
+          <t>31526</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20797</t>
+          <t>21163</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44382</t>
+          <t>43313</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>397246</t>
+          <t>398095</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>411081</t>
+          <t>411461</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>305886</t>
+          <t>304298</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>323709</t>
+          <t>322900</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>707868</t>
+          <t>708937</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>731453</t>
+          <t>731087</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22709</t>
+          <t>23281</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45187</t>
+          <t>45198</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7787</t>
+          <t>8399</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22558</t>
+          <t>24198</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34832</t>
+          <t>35063</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62361</t>
+          <t>61369</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>581185</t>
+          <t>581174</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>603663</t>
+          <t>603091</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>237571</t>
+          <t>235931</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>252342</t>
+          <t>251730</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>824141</t>
+          <t>825133</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>851670</t>
+          <t>851439</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53098</t>
+          <t>52536</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84234</t>
+          <t>85434</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44304</t>
+          <t>45371</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75394</t>
+          <t>76929</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>105219</t>
+          <t>105951</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>150490</t>
+          <t>152599</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1069846</t>
+          <t>1068646</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1100982</t>
+          <t>1101544</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>686989</t>
+          <t>685454</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>718079</t>
+          <t>717012</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1765973</t>
+          <t>1763864</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1811244</t>
+          <t>1810512</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,47%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24083</t>
+          <t>24549</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46419</t>
+          <t>46924</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41896</t>
+          <t>42872</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71067</t>
+          <t>72716</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72091</t>
+          <t>73101</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>108117</t>
+          <t>110369</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>463175</t>
+          <t>462670</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>485511</t>
+          <t>485045</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>686477</t>
+          <t>684828</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>715648</t>
+          <t>714672</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1159021</t>
+          <t>1156769</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1195047</t>
+          <t>1194037</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,23%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>4508</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16288</t>
+          <t>16236</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41842</t>
+          <t>42057</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>70340</t>
+          <t>71408</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50643</t>
+          <t>50286</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>82905</t>
+          <t>82678</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249280</t>
+          <t>249332</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261438</t>
+          <t>261060</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1034822</t>
+          <t>1033754</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1063320</t>
+          <t>1063105</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1287825</t>
+          <t>1288052</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1320087</t>
+          <t>1320444</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>139027</t>
+          <t>139429</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>191687</t>
+          <t>190120</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>193070</t>
+          <t>189736</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>251427</t>
+          <t>251860</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>343533</t>
+          <t>343925</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>421614</t>
+          <t>420090</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3217564</t>
+          <t>3219131</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3270224</t>
+          <t>3269822</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3284070</t>
+          <t>3283637</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3342427</t>
+          <t>3345761</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6523134</t>
+          <t>6524658</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6601215</t>
+          <t>6600823</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>3697</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15937</t>
+          <t>15284</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>7870</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24467</t>
+          <t>23842</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13826</t>
+          <t>14361</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33531</t>
+          <t>34513</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>412192</t>
+          <t>412845</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>424340</t>
+          <t>424432</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>320746</t>
+          <t>321371</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>337170</t>
+          <t>337343</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>739811</t>
+          <t>738829</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>759516</t>
+          <t>758981</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>6795</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20829</t>
+          <t>20252</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7872</t>
+          <t>8254</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23282</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17398</t>
+          <t>17904</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39985</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>352314</t>
+          <t>352891</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>366682</t>
+          <t>366348</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>347066</t>
+          <t>347362</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>362476</t>
+          <t>362094</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>703506</t>
+          <t>705080</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>726093</t>
+          <t>725587</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15352</t>
+          <t>15590</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36151</t>
+          <t>35463</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9863</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18455</t>
+          <t>18715</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41126</t>
+          <t>40980</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>480353</t>
+          <t>481041</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>501152</t>
+          <t>500914</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>156260</t>
+          <t>156045</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164965</t>
+          <t>165029</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>641501</t>
+          <t>641647</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>664172</t>
+          <t>663912</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34306</t>
+          <t>33047</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61766</t>
+          <t>61586</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31363</t>
+          <t>31854</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56520</t>
+          <t>57651</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71344</t>
+          <t>69576</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109199</t>
+          <t>107057</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1081878</t>
+          <t>1082058</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1109338</t>
+          <t>1110597</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>764261</t>
+          <t>763130</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>789418</t>
+          <t>788927</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1855226</t>
+          <t>1857368</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1893081</t>
+          <t>1894849</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22701</t>
+          <t>22956</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50094</t>
+          <t>48296</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37738</t>
+          <t>35723</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64565</t>
+          <t>62968</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66886</t>
+          <t>65705</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102754</t>
+          <t>103468</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>568830</t>
+          <t>570628</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>596223</t>
+          <t>595968</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>669208</t>
+          <t>670805</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>696035</t>
+          <t>698050</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1249943</t>
+          <t>1249229</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1285811</t>
+          <t>1286992</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12448</t>
+          <t>12165</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30772</t>
+          <t>31594</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25197</t>
+          <t>25188</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51153</t>
+          <t>49338</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43394</t>
+          <t>42557</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>73757</t>
+          <t>74224</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255261</t>
+          <t>254439</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>273585</t>
+          <t>273868</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1025873</t>
+          <t>1027688</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1051829</t>
+          <t>1051838</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1289302</t>
+          <t>1288835</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1319665</t>
+          <t>1320502</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>121007</t>
+          <t>124114</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>170070</t>
+          <t>174284</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>135480</t>
+          <t>135320</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>186277</t>
+          <t>186917</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>271569</t>
+          <t>272234</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>339396</t>
+          <t>339025</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3196306</t>
+          <t>3192092</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3245369</t>
+          <t>3242262</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3326988</t>
+          <t>3326348</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3377785</t>
+          <t>3377945</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6540245</t>
+          <t>6540616</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6608072</t>
+          <t>6607407</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>13789</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21258</t>
+          <t>22894</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9484</t>
+          <t>10733</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17258</t>
+          <t>18531</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>22793</t>
+          <t>24522</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14902</t>
+          <t>15686</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33654</t>
+          <t>35400</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>485197</t>
+          <t>530204</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>477249</t>
+          <t>521099</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>491518</t>
+          <t>536760</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>435536</t>
+          <t>475160</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>427762</t>
+          <t>467362</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>440429</t>
+          <t>479711</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>920735</t>
+          <t>1005364</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>909874</t>
+          <t>994486</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>928626</t>
+          <t>1014200</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>498507</t>
+          <t>543993</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>498507</t>
+          <t>543993</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>498507</t>
+          <t>543993</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>445020</t>
+          <t>485893</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>445020</t>
+          <t>485893</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>445020</t>
+          <t>485893</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>943528</t>
+          <t>1029886</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>943528</t>
+          <t>1029886</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>943528</t>
+          <t>1029886</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>8377</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15794</t>
+          <t>18371</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>9179</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11171</t>
+          <t>14926</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>12089</t>
+          <t>17555</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>10670</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22189</t>
+          <t>28149</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>442170</t>
+          <t>470775</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>432640</t>
+          <t>460781</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>446334</t>
+          <t>475681</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>370807</t>
+          <t>407752</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>365461</t>
+          <t>402005</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>373586</t>
+          <t>412046</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>812977</t>
+          <t>878528</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>802877</t>
+          <t>867934</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>818920</t>
+          <t>885413</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>448434</t>
+          <t>479152</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>448434</t>
+          <t>479152</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>448434</t>
+          <t>479152</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>376632</t>
+          <t>416931</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>376632</t>
+          <t>416931</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>376632</t>
+          <t>416931</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>825066</t>
+          <t>896083</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>825066</t>
+          <t>896083</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>825066</t>
+          <t>896083</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>10421</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21075</t>
+          <t>19555</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9929</t>
+          <t>10730</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>12948</t>
+          <t>15238</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4525</t>
+          <t>8383</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24567</t>
+          <t>24674</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>653549</t>
+          <t>456434</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>642678</t>
+          <t>447300</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>661061</t>
+          <t>461930</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>161133</t>
+          <t>178811</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153948</t>
+          <t>172898</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163201</t>
+          <t>182013</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>814682</t>
+          <t>635245</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>803063</t>
+          <t>625809</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>823105</t>
+          <t>642100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>663753</t>
+          <t>466855</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>663753</t>
+          <t>466855</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>663753</t>
+          <t>466855</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>163877</t>
+          <t>183628</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>163877</t>
+          <t>183628</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>163877</t>
+          <t>183628</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>827630</t>
+          <t>650483</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>827630</t>
+          <t>650483</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>827630</t>
+          <t>650483</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23210</t>
+          <t>33839</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15209</t>
+          <t>23204</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35837</t>
+          <t>49220</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16006</t>
+          <t>21472</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6684</t>
+          <t>15176</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25536</t>
+          <t>31256</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>39216</t>
+          <t>55311</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26632</t>
+          <t>41747</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54843</t>
+          <t>70896</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1010434</t>
+          <t>1096850</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>997807</t>
+          <t>1081469</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1018435</t>
+          <t>1107485</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>955702</t>
+          <t>831798</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>946172</t>
+          <t>822014</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>965024</t>
+          <t>838094</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1966136</t>
+          <t>1928649</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1950509</t>
+          <t>1913064</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1978720</t>
+          <t>1942213</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1033644</t>
+          <t>1130689</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1033644</t>
+          <t>1130689</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1033644</t>
+          <t>1130689</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>971708</t>
+          <t>853270</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>971708</t>
+          <t>853270</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>971708</t>
+          <t>853270</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2005352</t>
+          <t>1983960</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2005352</t>
+          <t>1983960</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2005352</t>
+          <t>1983960</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12390</t>
+          <t>18494</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6876</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21171</t>
+          <t>30010</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24514</t>
+          <t>33336</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16982</t>
+          <t>23995</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34975</t>
+          <t>43551</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>36904</t>
+          <t>51830</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26086</t>
+          <t>38620</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48749</t>
+          <t>65671</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>460484</t>
+          <t>547268</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>451703</t>
+          <t>535752</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>465998</t>
+          <t>554593</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>808606</t>
+          <t>790108</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>798145</t>
+          <t>779893</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>816138</t>
+          <t>799449</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1269089</t>
+          <t>1337376</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1257244</t>
+          <t>1323535</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1279907</t>
+          <t>1350586</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>472874</t>
+          <t>565762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>472874</t>
+          <t>565762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>472874</t>
+          <t>565762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>833120</t>
+          <t>823444</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>833120</t>
+          <t>823444</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>833120</t>
+          <t>823444</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1305993</t>
+          <t>1389206</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1305993</t>
+          <t>1389206</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1305993</t>
+          <t>1389206</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>26143</t>
+          <t>34343</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16787</t>
+          <t>22512</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45249</t>
+          <t>51763</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>29350</t>
+          <t>37196</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18371</t>
+          <t>24939</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49545</t>
+          <t>55903</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -10461,27 +10461,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>230013</t>
+          <t>226777</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>222158</t>
+          <t>219632</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>233220</t>
+          <t>229630</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>728509</t>
+          <t>802548</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>709403</t>
+          <t>785128</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>737865</t>
+          <t>814379</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>958522</t>
+          <t>1029325</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>938327</t>
+          <t>1010618</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>969501</t>
+          <t>1041582</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>233220</t>
+          <t>229630</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>233220</t>
+          <t>229630</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>233220</t>
+          <t>229630</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>754652</t>
+          <t>836891</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>754652</t>
+          <t>836891</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>754652</t>
+          <t>836891</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>987872</t>
+          <t>1066521</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>987872</t>
+          <t>1066521</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>987872</t>
+          <t>1066521</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>68585</t>
+          <t>87773</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50665</t>
+          <t>70355</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>91407</t>
+          <t>108206</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>84715</t>
+          <t>113880</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>64608</t>
+          <t>95658</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>108768</t>
+          <t>138602</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>153301</t>
+          <t>201652</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>126959</t>
+          <t>173842</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>183299</t>
+          <t>230467</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3281848</t>
+          <t>3328308</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3259026</t>
+          <t>3307875</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3299768</t>
+          <t>3345726</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3460294</t>
+          <t>3486178</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3436241</t>
+          <t>3461456</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3480401</t>
+          <t>3504400</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6742140</t>
+          <t>6814487</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6712142</t>
+          <t>6785672</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6768482</t>
+          <t>6842297</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3350433</t>
+          <t>3416081</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3350433</t>
+          <t>3416081</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3350433</t>
+          <t>3416081</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3545009</t>
+          <t>3600058</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3545009</t>
+          <t>3600058</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3545009</t>
+          <t>3600058</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6895441</t>
+          <t>7016139</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6895441</t>
+          <t>7016139</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6895441</t>
+          <t>7016139</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">

--- a/data/trans_orig/Hacinamiento_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2007 (tasa de respuesta: 99,71%)</t>
+          <t>Población según si en su vivienda residen dos o más personas por habitación en 2007 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2012 (tasa de respuesta: 99,62%)</t>
+          <t>Población según si en su vivienda residen dos o más personas por habitación en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2016 (tasa de respuesta: 99,47%)</t>
+          <t>Población según si en su vivienda residen dos o más personas por habitación en 2016 (tasa de respuesta: 99,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2023 (tasa de respuesta: 99,08%)</t>
+          <t>Población según si en su vivienda residen dos o más personas por habitación en 2023 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
